--- a/Data/R365Data/ItemCost/P062026ItemCost.xlsx
+++ b/Data/R365Data/ItemCost/P062026ItemCost.xlsx
@@ -4233,16 +4233,8 @@
           <t>Iced Oat Masala Chai</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Masala Chai</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Masala Chai</t>
-        </is>
-      </c>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Iced Oat Masala Chai</t>
@@ -4849,16 +4841,8 @@
           <t>Masala Chai - Oat Milk</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Masala Chai</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>Masala Chai</t>
-        </is>
-      </c>
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="n"/>
       <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Masala Chai - Oat Milk</t>
@@ -17557,16 +17541,8 @@
           <t>Masala Chai - Oat Milk</t>
         </is>
       </c>
-      <c r="D323" s="2" t="inlineStr">
-        <is>
-          <t>Masala Chai</t>
-        </is>
-      </c>
-      <c r="E323" s="2" t="inlineStr">
-        <is>
-          <t>Masala Chai</t>
-        </is>
-      </c>
+      <c r="D323" s="2" t="n"/>
+      <c r="E323" s="2" t="n"/>
       <c r="F323" s="2" t="inlineStr">
         <is>
           <t>Masala Chai - Oat Milk</t>
@@ -17613,16 +17589,8 @@
           <t>Iced Oat Masala Chai</t>
         </is>
       </c>
-      <c r="D324" s="2" t="inlineStr">
-        <is>
-          <t>Masala Chai</t>
-        </is>
-      </c>
-      <c r="E324" s="2" t="inlineStr">
-        <is>
-          <t>Masala Chai</t>
-        </is>
-      </c>
+      <c r="D324" s="2" t="n"/>
+      <c r="E324" s="2" t="n"/>
       <c r="F324" s="2" t="inlineStr">
         <is>
           <t>Iced Oat Masala Chai</t>
@@ -18337,16 +18305,8 @@
           <t>Iced Oat Masala Chai for a Group - 1/2 Gallon</t>
         </is>
       </c>
-      <c r="D337" s="2" t="inlineStr">
-        <is>
-          <t>Masala Chai</t>
-        </is>
-      </c>
-      <c r="E337" s="2" t="inlineStr">
-        <is>
-          <t>Masala Chai</t>
-        </is>
-      </c>
+      <c r="D337" s="2" t="n"/>
+      <c r="E337" s="2" t="n"/>
       <c r="F337" s="2" t="inlineStr">
         <is>
           <t>Iced Oat Masala Chai for a Group - 1/2 Gallon</t>
@@ -20281,16 +20241,8 @@
           <t>Iced Oat Masala Chai</t>
         </is>
       </c>
-      <c r="D372" s="2" t="inlineStr">
-        <is>
-          <t>Masala Chai</t>
-        </is>
-      </c>
-      <c r="E372" s="2" t="inlineStr">
-        <is>
-          <t>Masala Chai</t>
-        </is>
-      </c>
+      <c r="D372" s="2" t="n"/>
+      <c r="E372" s="2" t="n"/>
       <c r="F372" s="2" t="inlineStr">
         <is>
           <t>Iced Oat Masala Chai</t>
@@ -20393,16 +20345,8 @@
           <t>Masala Chai - Oat Milk</t>
         </is>
       </c>
-      <c r="D374" s="2" t="inlineStr">
-        <is>
-          <t>Masala Chai</t>
-        </is>
-      </c>
-      <c r="E374" s="2" t="inlineStr">
-        <is>
-          <t>Masala Chai</t>
-        </is>
-      </c>
+      <c r="D374" s="2" t="n"/>
+      <c r="E374" s="2" t="n"/>
       <c r="F374" s="2" t="inlineStr">
         <is>
           <t>Masala Chai - Oat Milk</t>
@@ -22014,66 +21958,66 @@
       <c r="Z407" s="2" t="n"/>
     </row>
     <row r="408">
-      <c r="A408" t="inlineStr">
+      <c r="A408" s="0" t="inlineStr">
         <is>
           <t>OFFSITE POP-UPS</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr">
+      <c r="C408" s="0" t="inlineStr">
         <is>
           <t>Spicy Chili Chicken Bowl</t>
         </is>
       </c>
-      <c r="F408" t="inlineStr">
+      <c r="F408" s="0" t="inlineStr">
         <is>
           <t>Spicy Chili Chicken Bowl</t>
         </is>
       </c>
-      <c r="G408" t="inlineStr">
+      <c r="G408" s="0" t="inlineStr">
         <is>
           <t>$0.6065</t>
         </is>
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="inlineStr">
+      <c r="A409" s="0" t="inlineStr">
         <is>
           <t>CATERING</t>
         </is>
       </c>
-      <c r="C409" t="inlineStr">
+      <c r="C409" s="0" t="inlineStr">
         <is>
           <t>Spicy Chicken Burrito</t>
         </is>
       </c>
-      <c r="F409" t="inlineStr">
+      <c r="F409" s="0" t="inlineStr">
         <is>
           <t>Spicy Chicken Burrito</t>
         </is>
       </c>
-      <c r="G409" t="inlineStr">
+      <c r="G409" s="0" t="inlineStr">
         <is>
           <t>$2.4901</t>
         </is>
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="inlineStr">
+      <c r="A410" s="0" t="inlineStr">
         <is>
           <t>Open items</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr">
+      <c r="C410" s="0" t="inlineStr">
         <is>
           <t>Spicy Chili Chicken</t>
         </is>
       </c>
-      <c r="F410" t="inlineStr">
+      <c r="F410" s="0" t="inlineStr">
         <is>
           <t>Spicy Chili Chicken</t>
         </is>
       </c>
-      <c r="G410" t="inlineStr">
+      <c r="G410" s="0" t="inlineStr">
         <is>
           <t>$0.6880</t>
         </is>
